--- a/data/trans_orig/LAWTONB_2R3-Clase-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R3-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8851</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>17344</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50933</t>
+          <t>50924</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58855</t>
+          <t>58845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17474</t>
+          <t>17829</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27504</t>
+          <t>27517</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72335</t>
+          <t>72149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84340</t>
+          <t>84537</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12990</t>
+          <t>13762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>905</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17157</t>
+          <t>16429</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37840</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48876</t>
+          <t>48729</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>14881</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49459</t>
+          <t>50187</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62592</t>
+          <t>62690</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>9783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20706</t>
+          <t>19621</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57754</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68189</t>
+          <t>68114</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23129</t>
+          <t>23114</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75324</t>
+          <t>76409</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88664</t>
+          <t>88746</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29732</t>
+          <t>29180</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51430</t>
+          <t>51111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40088</t>
+          <t>40368</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65783</t>
+          <t>64712</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>208642</t>
+          <t>208961</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>230340</t>
+          <t>230892</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64300</t>
+          <t>64556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78211</t>
+          <t>78112</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280041</t>
+          <t>281112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>305736</t>
+          <t>305456</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12486</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>16607</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34824</t>
+          <t>34238</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22428</t>
+          <t>21454</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>41342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42979</t>
+          <t>43229</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52599</t>
+          <t>52401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>62012</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79337</t>
+          <t>79643</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>108534</t>
+          <t>110373</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>129287</t>
+          <t>130261</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59192</t>
+          <t>59259</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91642</t>
+          <t>91117</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59976</t>
+          <t>60433</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91446</t>
+          <t>94146</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>333428</t>
+          <t>333953</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>365878</t>
+          <t>365811</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>337269</t>
+          <t>334569</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>368739</t>
+          <t>368282</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,9%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51582</t>
+          <t>51605</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80511</t>
+          <t>79900</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105642</t>
+          <t>105823</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>146624</t>
+          <t>147711</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169867</t>
+          <t>166564</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>216907</t>
+          <t>217279</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>421040</t>
+          <t>421651</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>449969</t>
+          <t>449946</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>530218</t>
+          <t>529131</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>571200</t>
+          <t>571019</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>961486</t>
+          <t>961114</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1008526</t>
+          <t>1011829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,87%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15279</t>
+          <t>15222</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31284</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42821</t>
+          <t>42806</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53928</t>
+          <t>53985</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66245</t>
+          <t>66137</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>15364</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20526</t>
+          <t>20772</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45878</t>
+          <t>45266</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57451</t>
+          <t>57471</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17787</t>
+          <t>17817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59005</t>
+          <t>58759</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73459</t>
+          <t>73367</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11028</t>
+          <t>9991</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28741</t>
+          <t>28700</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>19897</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43807</t>
+          <t>43102</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89912</t>
+          <t>89953</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107625</t>
+          <t>108662</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34754</t>
+          <t>34718</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47472</t>
+          <t>47475</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129461</t>
+          <t>130166</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>152689</t>
+          <t>152810</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,19%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48579</t>
+          <t>49794</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77096</t>
+          <t>78935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>8785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22016</t>
+          <t>22511</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63875</t>
+          <t>61759</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93872</t>
+          <t>95023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154657</t>
+          <t>152818</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183174</t>
+          <t>181959</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38079</t>
+          <t>37584</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51398</t>
+          <t>51310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>197976</t>
+          <t>196825</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227973</t>
+          <t>230089</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,84%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>13972</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>31372</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50460</t>
+          <t>50833</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76759</t>
+          <t>78608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71934</t>
+          <t>70496</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102783</t>
+          <t>103428</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70502</t>
+          <t>71324</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87218</t>
+          <t>88724</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111641</t>
+          <t>109792</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137940</t>
+          <t>137567</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>188313</t>
+          <t>187668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>219162</t>
+          <t>220600</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,78%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77576</t>
+          <t>79265</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>114280</t>
+          <t>115245</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>78081</t>
+          <t>79209</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112529</t>
+          <t>114188</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>280424</t>
+          <t>279459</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>317128</t>
+          <t>315439</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>284163</t>
+          <t>282504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>318611</t>
+          <t>317483</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,03%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97438</t>
+          <t>95353</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>137651</t>
+          <t>138893</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>170290</t>
+          <t>168159</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>218684</t>
+          <t>218593</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>281848</t>
+          <t>276183</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>343437</t>
+          <t>341217</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>421986</t>
+          <t>420744</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>462199</t>
+          <t>464284</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>523321</t>
+          <t>523412</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>571715</t>
+          <t>573846</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>958205</t>
+          <t>960425</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1019794</t>
+          <t>1025459</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,78%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>915</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15995</t>
+          <t>16596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57114</t>
+          <t>59103</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67149</t>
+          <t>67732</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26292</t>
+          <t>25839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35586</t>
+          <t>35610</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89540</t>
+          <t>88939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101219</t>
+          <t>101511</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13507</t>
+          <t>13398</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18188</t>
+          <t>17916</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39837</t>
+          <t>39946</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49840</t>
+          <t>49807</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16523</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52744</t>
+          <t>53016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65113</t>
+          <t>65214</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21637</t>
+          <t>20691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>17790</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14160</t>
+          <t>15641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32569</t>
+          <t>32923</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98624</t>
+          <t>99570</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112597</t>
+          <t>112670</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28175</t>
+          <t>28419</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41702</t>
+          <t>42318</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133901</t>
+          <t>133547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>152310</t>
+          <t>150829</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22392</t>
+          <t>21950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40618</t>
+          <t>41257</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32113</t>
+          <t>31473</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37426</t>
+          <t>37790</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63146</t>
+          <t>64102</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>163238</t>
+          <t>162599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>181464</t>
+          <t>181906</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66933</t>
+          <t>67573</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86697</t>
+          <t>86607</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>239756</t>
+          <t>238800</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>265476</t>
+          <t>265112</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25267</t>
+          <t>25233</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45104</t>
+          <t>45458</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28379</t>
+          <t>27723</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52920</t>
+          <t>51217</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59470</t>
+          <t>58123</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89598</t>
+          <t>88783</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100117</t>
+          <t>99763</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119954</t>
+          <t>119988</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>106630</t>
+          <t>108333</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131171</t>
+          <t>131827</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>215173</t>
+          <t>215988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>245301</t>
+          <t>246648</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83781</t>
+          <t>84972</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>123067</t>
+          <t>124211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>83781</t>
+          <t>84972</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123067</t>
+          <t>124211</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>290016</t>
+          <t>288872</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>329302</t>
+          <t>328111</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>290016</t>
+          <t>288872</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>329302</t>
+          <t>328111</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72292</t>
+          <t>74075</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106074</t>
+          <t>106225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>157358</t>
+          <t>154751</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>207800</t>
+          <t>206245</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>237596</t>
+          <t>241668</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>304012</t>
+          <t>300718</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>485254</t>
+          <t>485103</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>519036</t>
+          <t>517253</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>564564</t>
+          <t>566119</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>615006</t>
+          <t>617613</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1059680</t>
+          <t>1062974</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1126096</t>
+          <t>1122024</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,28%</t>
         </is>
       </c>
     </row>
@@ -8633,27 +8633,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7610</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12937</t>
+          <t>15078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>13837</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19704</t>
+          <t>21499</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -8746,22 +8746,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>101401</t>
+          <t>113647</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97505</t>
+          <t>109235</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103920</t>
+          <t>116516</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57711</t>
+          <t>66300</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52384</t>
+          <t>59481</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61303</t>
+          <t>70148</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>159112</t>
+          <t>179947</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152039</t>
+          <t>172285</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163638</t>
+          <t>184754</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106422</t>
+          <t>119225</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106422</t>
+          <t>119225</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106422</t>
+          <t>119225</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>171743</t>
+          <t>193784</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>171743</t>
+          <t>193784</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>171743</t>
+          <t>193784</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15701</t>
+          <t>17148</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>8053</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10673</t>
+          <t>13188</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,17 +9046,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16946</t>
+          <t>19112</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>13176</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24209</t>
+          <t>26475</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>84747</t>
+          <t>93655</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79297</t>
+          <t>87567</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89346</t>
+          <t>97970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>40236</t>
+          <t>47332</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36258</t>
+          <t>42197</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43092</t>
+          <t>50632</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,17 +9159,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>124983</t>
+          <t>140988</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>117720</t>
+          <t>133625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>130135</t>
+          <t>146924</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14843</t>
+          <t>15028</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10032</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21354</t>
+          <t>21446</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>16723</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>11720</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18980</t>
+          <t>22374</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29188</t>
+          <t>31751</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22738</t>
+          <t>24545</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36973</t>
+          <t>40699</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86644</t>
+          <t>96856</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80133</t>
+          <t>90438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91455</t>
+          <t>101677</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37424</t>
+          <t>40211</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32790</t>
+          <t>34560</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41717</t>
+          <t>45214</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>124069</t>
+          <t>137067</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116284</t>
+          <t>128119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130519</t>
+          <t>144273</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,46%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>101487</t>
+          <t>111884</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>101487</t>
+          <t>111884</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>101487</t>
+          <t>111884</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>56934</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>56934</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>56934</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>153257</t>
+          <t>168818</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>153257</t>
+          <t>168818</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>153257</t>
+          <t>168818</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51695</t>
+          <t>55097</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>43949</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61786</t>
+          <t>67256</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22653</t>
+          <t>24934</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>18860</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65278</t>
+          <t>31223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>74347</t>
+          <t>80031</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26671</t>
+          <t>68238</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122519</t>
+          <t>94779</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>184041</t>
+          <t>202227</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>173950</t>
+          <t>190068</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>194542</t>
+          <t>213375</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>304040</t>
+          <t>105946</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>261415</t>
+          <t>99657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>321022</t>
+          <t>112020</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>488082</t>
+          <t>308173</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>439910</t>
+          <t>293425</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>535758</t>
+          <t>319966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>82,42%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>235736</t>
+          <t>257324</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>235736</t>
+          <t>257324</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>235736</t>
+          <t>257324</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>562429</t>
+          <t>388204</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>562429</t>
+          <t>388204</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>562429</t>
+          <t>388204</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20490</t>
+          <t>21725</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>15794</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26891</t>
+          <t>28522</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>69783</t>
+          <t>74978</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60736</t>
+          <t>65397</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79073</t>
+          <t>84973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>96703</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80031</t>
+          <t>84224</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102249</t>
+          <t>108434</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>69942</t>
+          <t>77329</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63541</t>
+          <t>70532</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75320</t>
+          <t>83260</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>133626</t>
+          <t>143296</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124336</t>
+          <t>133301</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142673</t>
+          <t>152877</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>203569</t>
+          <t>220624</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>191592</t>
+          <t>208893</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>213810</t>
+          <t>233103</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,46%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>90432</t>
+          <t>99054</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90432</t>
+          <t>99054</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90432</t>
+          <t>99054</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>203409</t>
+          <t>218274</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>203409</t>
+          <t>218274</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203409</t>
+          <t>218274</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>293841</t>
+          <t>317327</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>293841</t>
+          <t>317327</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>293841</t>
+          <t>317327</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,27 +10348,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>108779</t>
+          <t>117371</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>96765</t>
+          <t>104196</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>122452</t>
+          <t>129775</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>110924</t>
+          <t>119575</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98595</t>
+          <t>107330</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>124074</t>
+          <t>134386</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>211071</t>
+          <t>226293</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>197398</t>
+          <t>213889</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>223085</t>
+          <t>239468</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>212130</t>
+          <t>227366</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>198980</t>
+          <t>212555</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>224459</t>
+          <t>239611</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,06%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>319850</t>
+          <t>343664</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>319850</t>
+          <t>343664</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>319850</t>
+          <t>343664</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>323054</t>
+          <t>346941</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>323054</t>
+          <t>346941</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>323054</t>
+          <t>346941</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>104444</t>
+          <t>110691</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90646</t>
+          <t>96594</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>120451</t>
+          <t>127590</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>229865</t>
+          <t>250317</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>116527</t>
+          <t>231330</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>294119</t>
+          <t>270621</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>334309</t>
+          <t>361008</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>208826</t>
+          <t>336657</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>390068</t>
+          <t>388253</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>527834</t>
+          <t>584787</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>511827</t>
+          <t>567888</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>541632</t>
+          <t>598884</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>784109</t>
+          <t>629379</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>719855</t>
+          <t>609075</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>897447</t>
+          <t>648366</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1311943</t>
+          <t>1214166</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1256184</t>
+          <t>1186921</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1437426</t>
+          <t>1238517</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>78,63%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>632278</t>
+          <t>695478</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>632278</t>
+          <t>695478</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>632278</t>
+          <t>695478</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1013974</t>
+          <t>879696</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1013974</t>
+          <t>879696</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1013974</t>
+          <t>879696</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1646252</t>
+          <t>1575174</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1646252</t>
+          <t>1575174</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1646252</t>
+          <t>1575174</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
